--- a/excel/Job-Allocation-Full.xlsx
+++ b/excel/Job-Allocation-Full.xlsx
@@ -8,13 +8,51 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\home\boyko\opt2026\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34867FC0-17B8-4187-8501-3560768DB5BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45A0FDAE-9FDA-4EC6-843D-AAF761F0B507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4452" yWindow="3660" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scores" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="solver_adj" localSheetId="0" hidden="1">Scores!$B$7:$D$9</definedName>
+    <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
+    <definedName name="solver_drv" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_lhs1" localSheetId="0" hidden="1">Scores!$B$10:$D$10</definedName>
+    <definedName name="solver_lhs2" localSheetId="0" hidden="1">Scores!$B$7:$D$9</definedName>
+    <definedName name="solver_lhs3" localSheetId="0" hidden="1">Scores!$E$7:$E$9</definedName>
+    <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
+    <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
+    <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_num" localSheetId="0" hidden="1">3</definedName>
+    <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_opt" localSheetId="0" hidden="1">Scores!$E$10</definedName>
+    <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
+    <definedName name="solver_rbv" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rel1" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rel2" localSheetId="0" hidden="1">5</definedName>
+    <definedName name="solver_rel3" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rhs1" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rhs2" localSheetId="0" hidden="1">"binary"</definedName>
+    <definedName name="solver_rhs3" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_scl" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_ssz" localSheetId="0" hidden="1">100</definedName>
+    <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
+    <definedName name="solver_typ" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -489,16 +527,18 @@
       <c r="A7" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="1"/>
+      <c r="B7" s="1">
+        <v>1</v>
+      </c>
       <c r="C7" s="1">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D7" s="1">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <f>SUM(B7:D7)</f>
-        <v>133</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
         <v>1</v>
@@ -509,17 +549,17 @@
         <v>4</v>
       </c>
       <c r="B8" s="1">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="C8" s="1">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="D8" s="1">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="E8">
         <f t="shared" ref="E8:E9" si="0">SUM(B8:D8)</f>
-        <v>147</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2">
         <v>1</v>
@@ -530,17 +570,17 @@
         <v>5</v>
       </c>
       <c r="B9" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C9" s="1">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="D9" s="1">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <f t="shared" si="0"/>
-        <v>127</v>
+        <v>1</v>
       </c>
       <c r="F9" s="2">
         <v>1</v>
@@ -549,19 +589,19 @@
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B10">
         <f>SUM(B7:B9)</f>
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="C10">
         <f t="shared" ref="C10:D10" si="1">SUM(C7:C9)</f>
-        <v>194</v>
+        <v>1</v>
       </c>
       <c r="D10">
         <f t="shared" si="1"/>
-        <v>173</v>
+        <v>1</v>
       </c>
       <c r="E10" s="3">
         <f>SUMPRODUCT(B7:D9,B2:D4)</f>
-        <v>24343</v>
+        <v>193</v>
       </c>
       <c r="F10" t="s">
         <v>8</v>
